--- a/stacked_model/results/baseline/baseline_controls_only_top10.xlsx
+++ b/stacked_model/results/baseline/baseline_controls_only_top10.xlsx
@@ -497,10 +497,10 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>91.74258967979463</v>
+        <v>91.7425896797956</v>
       </c>
       <c r="H2" t="n">
-        <v>9.009802198610462</v>
+        <v>9.009802198609554</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
@@ -528,13 +528,13 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>90.06981602005068</v>
+        <v>90.06981602005173</v>
       </c>
       <c r="H3" t="n">
-        <v>9.85485793246372</v>
+        <v>9.854857932462682</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9104318996847025</v>
+        <v>0.9104318996846936</v>
       </c>
     </row>
     <row r="4">
@@ -559,13 +559,13 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>90.24520500321567</v>
+        <v>90.24520500321636</v>
       </c>
       <c r="H4" t="n">
-        <v>9.160204551784455</v>
+        <v>9.160204551783549</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8795250610348001</v>
+        <v>0.8795250610347716</v>
       </c>
     </row>
     <row r="5">
@@ -590,13 +590,13 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>92.67172665235434</v>
+        <v>92.67172665235458</v>
       </c>
       <c r="H5" t="n">
-        <v>5.548446020966651</v>
+        <v>5.548446020966241</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8730513374814041</v>
+        <v>0.87305133748138</v>
       </c>
     </row>
     <row r="6">
@@ -621,13 +621,13 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>91.99861798254969</v>
+        <v>91.99861798255006</v>
       </c>
       <c r="H6" t="n">
-        <v>6.600198605183674</v>
+        <v>6.600198605183064</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8698040845840262</v>
+        <v>0.8698040845839985</v>
       </c>
     </row>
     <row r="7">
@@ -652,13 +652,13 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>89.41980399291042</v>
+        <v>89.4198039929116</v>
       </c>
       <c r="H7" t="n">
-        <v>10.0175887838013</v>
+        <v>10.01758878380028</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8696184009877788</v>
+        <v>0.8696184009877781</v>
       </c>
     </row>
     <row r="8">
@@ -683,13 +683,13 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>89.53083789477527</v>
+        <v>89.53083789477625</v>
       </c>
       <c r="H8" t="n">
-        <v>9.877889721312737</v>
+        <v>9.877889721311668</v>
       </c>
       <c r="I8" t="n">
-        <v>0.869160662628951</v>
+        <v>0.8691606626289327</v>
       </c>
     </row>
     <row r="9">
@@ -714,13 +714,13 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>89.54406129959926</v>
+        <v>89.5440612996003</v>
       </c>
       <c r="H9" t="n">
-        <v>9.860568490834067</v>
+        <v>9.860568490832996</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8690656606071049</v>
+        <v>0.869065660607091</v>
       </c>
     </row>
     <row r="10">
@@ -745,13 +745,13 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>90.77406497324741</v>
+        <v>90.77406497324782</v>
       </c>
       <c r="H10" t="n">
-        <v>8.263901657915735</v>
+        <v>8.263901657914843</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8654975949588295</v>
+        <v>0.8654975949587819</v>
       </c>
     </row>
     <row r="11">
@@ -776,13 +776,13 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>92.57526345946627</v>
+        <v>92.57526345946644</v>
       </c>
       <c r="H11" t="n">
-        <v>5.527255766739317</v>
+        <v>5.527255766738929</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8614905611949827</v>
+        <v>0.8614905611949526</v>
       </c>
     </row>
   </sheetData>
